--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113706038</v>
+        <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>58790</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Garpenberg, Dlr</t>
+          <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567128</v>
+        <v>567100</v>
       </c>
       <c r="R2" t="n">
-        <v>6686840</v>
+        <v>6686861</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,20 +765,1065 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136683139</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136683194</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92105</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>567158</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6686873</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136683194</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136682849</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96557</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Piparmossen, Piparmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567126</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6686820</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136682849</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136682950</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567122</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6686875</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136682950</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136683623</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92498</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4877</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis/erubescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Piparmossen, Piparmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>567315</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6686858</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136683623</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136683258</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>567158</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6686873</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136683258</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136683576</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567298</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6686891</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136683576</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136683692</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>567304</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6686863</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136683692</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136682966</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567100</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6686861</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136682966</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136683367</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>567168</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6686835</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136683367</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113706038</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Garpenberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>567128</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6686840</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Lisa Sandberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Johan Engström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113706038</t>
         </is>
@@ -791,6 +1832,16 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92499</v>
+        <v>92504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,7 +1189,7 @@
         <v>136683258</v>
       </c>
       <c r="B7" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,7 +1296,7 @@
         <v>136683576</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92504</v>
+        <v>92506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92506</v>
+        <v>92508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92508</v>
+        <v>92510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92510</v>
+        <v>92511</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92511</v>
+        <v>92517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92517</v>
+        <v>92521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92521</v>
+        <v>92523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92523</v>
+        <v>92536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>136683258</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>136683576</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>136683258</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>136683576</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -1215,11 +1215,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
@@ -1322,11 +1318,7 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
@@ -1429,11 +1421,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
@@ -1536,11 +1524,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>
@@ -1643,11 +1627,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Strångelsbogruvan, Strångelsbogruvan, Dlr</t>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92538</v>
+        <v>92541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92541</v>
+        <v>92551</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>136683258</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>136683576</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136683692</v>
       </c>
       <c r="B9" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>136682966</v>
       </c>
       <c r="B10" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136683367</v>
       </c>
       <c r="B11" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92551</v>
+        <v>92552</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>136683258</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>136683576</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34102-2026 artfynd.xlsx
+++ b/artfynd/A 34102-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136683139</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136683194</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136682849</v>
       </c>
       <c r="B4" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136682950</v>
       </c>
       <c r="B5" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136683623</v>
       </c>
       <c r="B6" t="n">
-        <v>92555</v>
+        <v>92557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
